--- a/Train Automation System/Grading/1 stage/3-examples/Train-Automation-System_Grading_1-stage_2026-02-28_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Train Automation System/Grading/1 stage/3-examples/Train-Automation-System_Grading_1-stage_2026-02-28_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Train Automation System/Grading/1 stage/2026-02-28/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Train Automation System/Grading/1 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF988477-BA73-BD4C-8150-5B1A2031C1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEEDBD7-7B0C-6046-AC35-A9F1364B19C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train Automation System" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="206">
   <si>
     <t>Type</t>
   </si>
@@ -301,16 +301,10 @@
     <t>AtStation composite state exists but is not the initial state of train movement</t>
   </si>
   <si>
-    <t>Entry Action</t>
-  </si>
-  <si>
     <t>openDoors()</t>
   </si>
   <si>
     <t>openDoors() action exists but on transition to AtStation rather than as entry action</t>
-  </si>
-  <si>
-    <t>Exit Action</t>
   </si>
   <si>
     <t>closeDoors()</t>
@@ -1236,18 +1230,18 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12636,30 +12630,30 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>87</v>
       </c>
       <c r="C11" s="22">
         <v>0.5</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="22">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>89</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="22">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12673,7 +12667,7 @@
         <v>0.5</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12687,7 +12681,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12701,7 +12695,7 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12715,7 +12709,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -12729,7 +12723,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -12761,21 +12755,21 @@
         <v>0</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C19" s="22">
         <v>0.5</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12789,7 +12783,7 @@
         <v>0.5</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12803,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12817,7 +12811,7 @@
         <v>0.5</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12831,7 +12825,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -12863,7 +12857,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12877,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -12891,7 +12885,7 @@
         <v>0.5</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12905,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12919,21 +12913,21 @@
         <v>1</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C29" s="22">
         <v>1</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12947,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -12979,7 +12973,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -13011,7 +13005,7 @@
         <v>0.5</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13025,21 +13019,21 @@
         <v>1</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C34" s="22">
         <v>1</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13053,7 +13047,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13067,7 +13061,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13081,7 +13075,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -13095,7 +13089,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -13127,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -13159,7 +13153,7 @@
         <v>0.5</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -13191,7 +13185,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -13223,7 +13217,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -13255,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -13287,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -13319,7 +13313,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -13351,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -13383,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -13415,7 +13409,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13429,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13443,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13457,7 +13451,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13471,7 +13465,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13485,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13499,7 +13493,7 @@
         <v>0</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13513,7 +13507,7 @@
         <v>0</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13527,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13541,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13555,7 +13549,7 @@
         <v>0</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13569,7 +13563,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13583,7 +13577,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13597,7 +13591,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13611,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13625,7 +13619,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13639,7 +13633,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13653,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13667,7 +13661,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13681,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13695,7 +13689,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13709,7 +13703,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13723,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13737,7 +13731,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13751,7 +13745,7 @@
         <v>2</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13765,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13779,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13793,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13807,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13821,7 +13815,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -13835,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18521,18 +18515,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
       <c r="J1" s="24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18540,28 +18534,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="E2" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="F2" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="G2" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="H2" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="J2" s="26" t="s">
         <v>161</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -18631,7 +18625,7 @@
         <v>0.7407407407407407</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18667,7 +18661,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="J5" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18804,7 +18798,7 @@
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B10" s="28">
         <f t="shared" ref="B10:E10" si="3">SUM(B3:B9)</f>
@@ -18846,46 +18840,46 @@
       <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
+      <c r="A12" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="E13" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="F13" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="G13" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="H13" s="25" t="s">
         <v>160</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" s="28">
         <f>COUNTIF('Train Automation System'!$A$2:$A$71, A14)</f>
@@ -18992,7 +18986,7 @@
       </c>
       <c r="C17" s="28">
         <f>SUMIF('LLM Grading'!$A$2:$A$71, $A17, 'LLM Grading'!$C$2:$C$71)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="28">
         <f>SUMIF('LLM Grading'!$A$72:$A$78, $A17, 'LLM Grading'!$C$72:$C$78)</f>
@@ -19000,19 +18994,19 @@
       </c>
       <c r="E17" s="28">
         <f>COUNTIFS('LLM Grading'!$A$2:$A$71, $A17, 'LLM Grading'!$C$2:$C$71,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" s="28">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G17" s="28">
         <f t="shared" si="5"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="28">
         <f t="shared" si="6"/>
-        <v>0.375</v>
+        <v>0.63157894736842102</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19116,7 +19110,7 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B21" s="30">
         <f t="shared" ref="B21:E21" si="7">SUM(B14:B20)</f>
@@ -19124,7 +19118,7 @@
       </c>
       <c r="C21" s="30">
         <f t="shared" si="7"/>
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="D21" s="30">
         <f t="shared" si="7"/>
@@ -19132,19 +19126,19 @@
       </c>
       <c r="E21" s="30">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21" s="28">
         <f t="shared" si="4"/>
-        <v>0.91549295774647887</v>
+        <v>0.92207792207792205</v>
       </c>
       <c r="G21" s="28">
         <f t="shared" si="5"/>
-        <v>0.4642857142857143</v>
+        <v>0.50714285714285712</v>
       </c>
       <c r="H21" s="31">
         <f t="shared" si="6"/>
-        <v>0.61611374407582942</v>
+        <v>0.65437788018433185</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20170,25 +20164,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E1" s="23"/>
-      <c r="F1" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="F1" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
-      <c r="L1" s="69" t="s">
-        <v>169</v>
-      </c>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
+      <c r="L1" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="35" t="str">
@@ -20209,29 +20203,29 @@
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="I2" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="J2" s="39" t="s">
         <v>172</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>174</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M2" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N2" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M2" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N2" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20273,14 +20267,14 @@
       </c>
       <c r="K3" s="23"/>
       <c r="L3" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M3" s="43">
         <f>(G3+H4+I5)/COUNTA($C$2:$C$125)</f>
         <v>0.4935064935064935</v>
       </c>
       <c r="N3" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20322,14 +20316,14 @@
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M4" s="46">
         <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$125), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$125))</f>
         <v>0.37949063923089893</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20371,14 +20365,14 @@
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M5" s="48">
         <f>(M3-M4)/(1-M4)</f>
         <v>0.18374558303886931</v>
       </c>
       <c r="N5" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20400,7 +20394,7 @@
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G6" s="16">
         <f t="shared" ref="G6:I6" si="2">SUM(G3:G5)</f>
@@ -20466,19 +20460,19 @@
         <v>0</v>
       </c>
       <c r="E8" s="23"/>
-      <c r="F8" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
+      <c r="F8" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
-      <c r="L8" s="69" t="s">
-        <v>185</v>
-      </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
+      <c r="L8" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="41" t="str">
@@ -20502,26 +20496,26 @@
         <v>4</v>
       </c>
       <c r="G9" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="J9" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I9" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M9" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N9" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M9" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N9" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20563,14 +20557,14 @@
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M10" s="43">
         <f>(G10+H11+I12)/COUNTIF($A$2:$A$125,F9)</f>
         <v>0.3888888888888889</v>
       </c>
       <c r="N10" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20612,14 +20606,14 @@
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M11" s="46">
         <f t="array" ref="M11">SUMPRODUCT(J10:J12/COUNTIF($A$2:$A$125,F9), TRANSPOSE(G13:I13)/COUNTIF($A$2:$A$125,F9))</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20661,14 +20655,14 @@
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M12" s="48">
         <f>(M10-M11)/(1-M11)</f>
         <v>8.3333333333333356E-2</v>
       </c>
       <c r="N12" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20690,7 +20684,7 @@
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G13" s="16">
         <f t="shared" ref="G13:I13" si="6">SUM(G10:G12)</f>
@@ -20756,19 +20750,19 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="F15" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
-      <c r="L15" s="69" t="s">
-        <v>187</v>
-      </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
+      <c r="L15" s="70" t="s">
+        <v>185</v>
+      </c>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="35" t="str">
@@ -20792,26 +20786,26 @@
         <v>7</v>
       </c>
       <c r="G16" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="J16" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I16" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J16" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M16" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N16" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N16" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20853,14 +20847,14 @@
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M17" s="43">
         <f>(G17+H18+I19)/COUNTIF($A$2:$A$125,F16)</f>
         <v>0.23809523809523808</v>
       </c>
       <c r="N17" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20902,14 +20896,14 @@
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M18" s="46">
         <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$125,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$125,F16))</f>
         <v>0.33786848072562353</v>
       </c>
       <c r="N18" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20951,14 +20945,14 @@
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M19" s="48">
         <f>(M17-M18)/(1-M18)</f>
         <v>-0.15068493150684925</v>
       </c>
       <c r="N19" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20980,7 +20974,7 @@
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="16">
         <f t="shared" ref="G20:I20" si="10">SUM(G17:G19)</f>
@@ -21046,19 +21040,19 @@
         <v>0.5</v>
       </c>
       <c r="E22" s="23"/>
-      <c r="F22" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+      <c r="F22" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
-      <c r="L22" s="69" t="s">
-        <v>189</v>
-      </c>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
+      <c r="L22" s="70" t="s">
+        <v>187</v>
+      </c>
+      <c r="M22" s="71"/>
+      <c r="N22" s="71"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="41" t="str">
@@ -21082,26 +21076,26 @@
         <v>11</v>
       </c>
       <c r="G23" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="J23" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I23" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M23" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N23" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M23" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N23" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21143,14 +21137,14 @@
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M24" s="43">
         <f>(G24+H25+I26)/COUNTIF($A$2:$A$125,F23)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="N24" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21192,14 +21186,14 @@
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M25" s="46">
         <f t="array" ref="M25">SUMPRODUCT(J24:J26/COUNTIF($A$2:$A$125,F23), TRANSPOSE(G27:I27)/COUNTIF($A$2:$A$125,F23))</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="N25" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21241,14 +21235,14 @@
       </c>
       <c r="K26" s="23"/>
       <c r="L26" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M26" s="48">
         <f>(M24-M25)/(1-M25)</f>
         <v>0.39999999999999997</v>
       </c>
       <c r="N26" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21270,7 +21264,7 @@
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G27" s="16">
         <f t="shared" ref="G27:I27" si="14">SUM(G24:G26)</f>
@@ -21336,19 +21330,19 @@
         <v>1</v>
       </c>
       <c r="E29" s="23"/>
-      <c r="F29" s="67" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
+      <c r="F29" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
       <c r="J29" s="23"/>
       <c r="K29" s="23"/>
-      <c r="L29" s="69" t="s">
-        <v>191</v>
-      </c>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
+      <c r="L29" s="70" t="s">
+        <v>189</v>
+      </c>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="35" t="str">
@@ -21372,26 +21366,26 @@
         <v>21</v>
       </c>
       <c r="G30" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I30" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H30" s="52" t="s">
+      <c r="J30" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I30" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M30" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N30" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M30" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N30" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21433,14 +21427,14 @@
       </c>
       <c r="K31" s="23"/>
       <c r="L31" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M31" s="43">
         <f>(G31+H32+I33)/COUNTIF($A$2:$A$125,F30)</f>
         <v>0.46666666666666667</v>
       </c>
       <c r="N31" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21482,14 +21476,14 @@
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M32" s="46">
         <f t="array" ref="M32">SUMPRODUCT(J31:J33/COUNTIF($A$2:$A$125,F30), TRANSPOSE(G34:I34)/COUNTIF($A$2:$A$125,F30))</f>
         <v>0.4</v>
       </c>
       <c r="N32" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21531,14 +21525,14 @@
       </c>
       <c r="K33" s="23"/>
       <c r="L33" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M33" s="48">
         <f>(M31-M32)/(1-M32)</f>
         <v>0.11111111111111109</v>
       </c>
       <c r="N33" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21560,7 +21554,7 @@
       </c>
       <c r="E34" s="23"/>
       <c r="F34" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G34" s="16">
         <f t="shared" ref="G34:I34" si="18">SUM(G31:G33)</f>
@@ -21626,19 +21620,19 @@
         <v>0</v>
       </c>
       <c r="E36" s="23"/>
-      <c r="F36" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+      <c r="F36" s="66" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
       <c r="J36" s="23"/>
       <c r="K36" s="23"/>
-      <c r="L36" s="69" t="s">
-        <v>193</v>
-      </c>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
+      <c r="L36" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="M36" s="71"/>
+      <c r="N36" s="71"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="41" t="str">
@@ -21662,26 +21656,26 @@
         <v>9</v>
       </c>
       <c r="G37" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="I37" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="H37" s="54" t="s">
+      <c r="J37" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I37" s="54" t="s">
-        <v>173</v>
-      </c>
-      <c r="J37" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M37" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N37" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M37" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N37" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21723,14 +21717,14 @@
       </c>
       <c r="K38" s="23"/>
       <c r="L38" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M38" s="43">
         <f>(G38+H39+I40)/COUNTIF($A$2:$A$125,F37)</f>
         <v>0.61538461538461542</v>
       </c>
       <c r="N38" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21772,14 +21766,14 @@
       </c>
       <c r="K39" s="23"/>
       <c r="L39" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M39" s="46">
         <f t="array" ref="M39">SUMPRODUCT(J38:J40/COUNTIF($A$2:$A$125,F37), TRANSPOSE(G41:I41)/COUNTIF($A$2:$A$125,F37))</f>
         <v>0.41420118343195267</v>
       </c>
       <c r="N39" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21821,14 +21815,14 @@
       </c>
       <c r="K40" s="23"/>
       <c r="L40" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M40" s="48">
         <f>(M38-M39)/(1-M39)</f>
         <v>0.34343434343434348</v>
       </c>
       <c r="N40" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21850,7 +21844,7 @@
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G41" s="16">
         <f>SUM(G38:G40)</f>
@@ -21916,19 +21910,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="23"/>
-      <c r="F43" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
+      <c r="F43" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
+      <c r="I43" s="67"/>
       <c r="J43" s="23"/>
       <c r="K43" s="23"/>
-      <c r="L43" s="69" t="s">
-        <v>195</v>
-      </c>
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
+      <c r="L43" s="70" t="s">
+        <v>193</v>
+      </c>
+      <c r="M43" s="71"/>
+      <c r="N43" s="71"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="35" t="str">
@@ -21952,26 +21946,26 @@
         <v>42</v>
       </c>
       <c r="G44" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H44" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I44" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H44" s="52" t="s">
+      <c r="J44" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I44" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J44" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M44" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N44" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M44" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N44" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22013,14 +22007,14 @@
       </c>
       <c r="K45" s="23"/>
       <c r="L45" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M45" s="43">
         <f>(G45+H46+I47)/COUNTIF($A$2:$A$125,F44)</f>
         <v>1</v>
       </c>
       <c r="N45" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22062,14 +22056,14 @@
       </c>
       <c r="K46" s="23"/>
       <c r="L46" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M46" s="46">
         <f t="array" ref="M46">SUMPRODUCT(J45:J47/COUNTIF($A$2:$A$125,F44), TRANSPOSE(G48:I48)/COUNTIF($A$2:$A$125,F44))</f>
         <v>1</v>
       </c>
       <c r="N46" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22111,14 +22105,14 @@
       </c>
       <c r="K47" s="23"/>
       <c r="L47" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M47" s="48" t="e">
         <f>(M45-M46)/(1-M46)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N47" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22140,7 +22134,7 @@
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G48" s="16">
         <f t="shared" ref="G48:I48" si="23">SUM(G45:G47)</f>
@@ -22206,19 +22200,19 @@
         <v>0</v>
       </c>
       <c r="E50" s="23"/>
-      <c r="F50" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
+      <c r="F50" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" s="67"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="67"/>
       <c r="J50" s="23"/>
       <c r="K50" s="23"/>
-      <c r="L50" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
+      <c r="L50" s="70" t="s">
+        <v>195</v>
+      </c>
+      <c r="M50" s="71"/>
+      <c r="N50" s="71"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="41" t="str">
@@ -22242,26 +22236,26 @@
         <v>13</v>
       </c>
       <c r="G51" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H51" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I51" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H51" s="52" t="s">
+      <c r="J51" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I51" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J51" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K51" s="23"/>
       <c r="L51" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="M51" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="N51" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="M51" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="N51" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22303,14 +22297,14 @@
       </c>
       <c r="K52" s="23"/>
       <c r="L52" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M52" s="43">
         <f>(G52+H53+I54)/COUNTIF($A$2:$A$125,F51)</f>
         <v>1</v>
       </c>
       <c r="N52" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22352,14 +22346,14 @@
       </c>
       <c r="K53" s="23"/>
       <c r="L53" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M53" s="46">
         <f t="array" ref="M53">SUMPRODUCT(J52:J54/COUNTIF($A$2:$A$125,F51), TRANSPOSE(G55:I55)/COUNTIF($A$2:$A$125,F51))</f>
         <v>0.68000000000000016</v>
       </c>
       <c r="N53" s="47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22401,14 +22395,14 @@
       </c>
       <c r="K54" s="23"/>
       <c r="L54" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M54" s="48">
         <f>(M52-M53)/(1-M53)</f>
         <v>1</v>
       </c>
       <c r="N54" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -22430,7 +22424,7 @@
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G55" s="16">
         <f t="shared" ref="G55:I55" si="27">SUM(G52:G54)</f>
@@ -24049,6 +24043,12 @@
     <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -24059,12 +24059,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -24106,26 +24100,26 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E1" s="23"/>
-      <c r="F1" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="F1" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
-      <c r="L1" s="67" t="s">
-        <v>198</v>
-      </c>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
+      <c r="L1" s="66" t="s">
+        <v>196</v>
+      </c>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
       <c r="P1" s="23"/>
       <c r="Q1" s="23"/>
       <c r="R1" s="23"/>
@@ -24155,45 +24149,45 @@
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="I2" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="J2" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="J2" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M2" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="N2" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="O2" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="N2" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="O2" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="P2" s="23"/>
       <c r="Q2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R2" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S2" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R2" s="52" t="s">
+      <c r="T2" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S2" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T2" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U2" s="23"/>
       <c r="V2" s="62" t="str">
@@ -24201,10 +24195,10 @@
         <v>Metrics Global</v>
       </c>
       <c r="W2" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X2" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24278,14 +24272,14 @@
       </c>
       <c r="U3" s="23"/>
       <c r="V3" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W3" s="43">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
         <v>0.36538461538461536</v>
       </c>
       <c r="X3" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24359,14 +24353,14 @@
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W4" s="46">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
         <v>0.4860289283366207</v>
       </c>
       <c r="X4" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24440,14 +24434,14 @@
       </c>
       <c r="U5" s="23"/>
       <c r="V5" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W5" s="48">
         <f>1-W3/W4</f>
         <v>0.24822455191072046</v>
       </c>
       <c r="X5" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24469,7 +24463,7 @@
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G6" s="16">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
@@ -24558,12 +24552,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="23"/>
-      <c r="F8" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
+      <c r="F8" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
@@ -24602,42 +24596,42 @@
         <v>4</v>
       </c>
       <c r="G9" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="J9" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I9" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M9" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="N9" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="52" t="s">
+      <c r="O9" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="N9" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="O9" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="P9" s="23"/>
       <c r="Q9" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R9" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S9" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R9" s="52" t="s">
+      <c r="T9" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S9" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T9" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U9" s="23"/>
       <c r="V9" s="62" t="str">
@@ -24645,10 +24639,10 @@
         <v>Metrics State</v>
       </c>
       <c r="W9" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X9" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24722,14 +24716,14 @@
       </c>
       <c r="U10" s="23"/>
       <c r="V10" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W10" s="43">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
         <v>0.44117647058823528</v>
       </c>
       <c r="X10" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24803,14 +24797,14 @@
       </c>
       <c r="U11" s="23"/>
       <c r="V11" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W11" s="46">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
         <v>0.49307958477508657</v>
       </c>
       <c r="X11" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24884,14 +24878,14 @@
       </c>
       <c r="U12" s="23"/>
       <c r="V12" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W12" s="48">
         <f>1-W10/W11</f>
         <v>0.10526315789473695</v>
       </c>
       <c r="X12" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -24913,7 +24907,7 @@
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G13" s="16">
         <f t="shared" ref="G13:I13" si="18">SUM(G10:G12)</f>
@@ -25002,12 +24996,12 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="F15" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -25046,42 +25040,42 @@
         <v>7</v>
       </c>
       <c r="G16" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="J16" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I16" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J16" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="N16" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M16" s="52" t="s">
+      <c r="O16" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="N16" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="O16" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="P16" s="23"/>
       <c r="Q16" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R16" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S16" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R16" s="52" t="s">
+      <c r="T16" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S16" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T16" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U16" s="23"/>
       <c r="V16" s="62" t="str">
@@ -25089,10 +25083,10 @@
         <v>Metrics Transition</v>
       </c>
       <c r="W16" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X16" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25166,14 +25160,14 @@
       </c>
       <c r="U17" s="23"/>
       <c r="V17" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W17" s="43">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
         <v>0.47619047619047616</v>
       </c>
       <c r="X17" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25247,14 +25241,14 @@
       </c>
       <c r="U18" s="23"/>
       <c r="V18" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W18" s="46">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
         <v>0.42630385487528344</v>
       </c>
       <c r="X18" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25328,14 +25322,14 @@
       </c>
       <c r="U19" s="23"/>
       <c r="V19" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W19" s="48">
         <f>1-W17/W18</f>
         <v>-0.11702127659574457</v>
       </c>
       <c r="X19" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25357,7 +25351,7 @@
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="16">
         <f t="shared" ref="G20:I20" si="28">SUM(G17:G19)</f>
@@ -25446,12 +25440,12 @@
         <v>0.5</v>
       </c>
       <c r="E22" s="23"/>
-      <c r="F22" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+      <c r="F22" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
@@ -25490,42 +25484,42 @@
         <v>11</v>
       </c>
       <c r="G23" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="J23" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I23" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M23" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="N23" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M23" s="52" t="s">
+      <c r="O23" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="N23" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="O23" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="P23" s="23"/>
       <c r="Q23" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R23" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S23" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R23" s="52" t="s">
+      <c r="T23" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S23" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T23" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U23" s="23"/>
       <c r="V23" s="62" t="str">
@@ -25533,10 +25527,10 @@
         <v>Metrics Composite State</v>
       </c>
       <c r="W23" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X23" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25610,14 +25604,14 @@
       </c>
       <c r="U24" s="23"/>
       <c r="V24" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W24" s="43">
         <f>SUMPRODUCT(G24:I26, M24:O26) /$J$27</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="X24" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25691,14 +25685,14 @@
       </c>
       <c r="U25" s="23"/>
       <c r="V25" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W25" s="46">
         <f>SUMPRODUCT(R24:T26, M24:O26)</f>
         <v>0.55555555555555558</v>
       </c>
       <c r="X25" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25772,14 +25766,14 @@
       </c>
       <c r="U26" s="23"/>
       <c r="V26" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W26" s="48">
         <f>1-W24/W25</f>
         <v>0.4</v>
       </c>
       <c r="X26" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -25801,7 +25795,7 @@
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G27" s="16">
         <f t="shared" ref="G27:I27" si="38">SUM(G24:G26)</f>
@@ -25890,12 +25884,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="23"/>
-      <c r="F29" s="67" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
+      <c r="F29" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
       <c r="J29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
@@ -25934,42 +25928,42 @@
         <v>21</v>
       </c>
       <c r="G30" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I30" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H30" s="52" t="s">
+      <c r="J30" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I30" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M30" s="52">
+        <v>0</v>
+      </c>
+      <c r="N30" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M30" s="52">
-        <v>0</v>
-      </c>
-      <c r="N30" s="52" t="s">
-        <v>172</v>
-      </c>
       <c r="O30" s="52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P30" s="23"/>
       <c r="Q30" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R30" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S30" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R30" s="52" t="s">
+      <c r="T30" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S30" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T30" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U30" s="23"/>
       <c r="V30" s="62" t="str">
@@ -25977,10 +25971,10 @@
         <v>Metrics Guard</v>
       </c>
       <c r="W30" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X30" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26054,14 +26048,14 @@
       </c>
       <c r="U31" s="23"/>
       <c r="V31" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W31" s="43">
         <f>SUMPRODUCT(G31:I33, M31:O33) /$J$34</f>
         <v>0.43333333333333335</v>
       </c>
       <c r="X31" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26135,14 +26129,14 @@
       </c>
       <c r="U32" s="23"/>
       <c r="V32" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W32" s="46">
         <f>SUMPRODUCT(R31:T33, M31:O33)</f>
         <v>0.5</v>
       </c>
       <c r="X32" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26216,14 +26210,14 @@
       </c>
       <c r="U33" s="23"/>
       <c r="V33" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W33" s="48">
         <f>1-W31/W32</f>
         <v>0.1333333333333333</v>
       </c>
       <c r="X33" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26245,7 +26239,7 @@
       </c>
       <c r="E34" s="23"/>
       <c r="F34" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G34" s="16">
         <f t="shared" ref="G34:I34" si="48">SUM(G31:G33)</f>
@@ -26334,12 +26328,12 @@
         <v>0</v>
       </c>
       <c r="E36" s="23"/>
-      <c r="F36" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+      <c r="F36" s="66" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
       <c r="J36" s="23"/>
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
@@ -26378,42 +26372,42 @@
         <v>9</v>
       </c>
       <c r="G37" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="I37" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="H37" s="54" t="s">
+      <c r="J37" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I37" s="54" t="s">
-        <v>173</v>
-      </c>
-      <c r="J37" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M37" s="52">
+        <v>0</v>
+      </c>
+      <c r="N37" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M37" s="52">
-        <v>0</v>
-      </c>
-      <c r="N37" s="52" t="s">
-        <v>172</v>
-      </c>
       <c r="O37" s="52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P37" s="23"/>
       <c r="Q37" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R37" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S37" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R37" s="52" t="s">
+      <c r="T37" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S37" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T37" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U37" s="23"/>
       <c r="V37" s="62" t="str">
@@ -26421,10 +26415,10 @@
         <v>Metrics Action</v>
       </c>
       <c r="W37" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X37" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26498,14 +26492,14 @@
       </c>
       <c r="U38" s="23"/>
       <c r="V38" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W38" s="43">
         <f>SUMPRODUCT(G38:I40, M38:O40) /$J$41</f>
         <v>0.26923076923076922</v>
       </c>
       <c r="X38" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26579,14 +26573,14 @@
       </c>
       <c r="U39" s="23"/>
       <c r="V39" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W39" s="46">
         <f>SUMPRODUCT(R38:T40, M38:O40)</f>
         <v>0.48224852071005919</v>
       </c>
       <c r="X39" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26660,14 +26654,14 @@
       </c>
       <c r="U40" s="23"/>
       <c r="V40" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W40" s="48">
         <f>1-W38/W39</f>
         <v>0.44171779141104295</v>
       </c>
       <c r="X40" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26689,7 +26683,7 @@
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G41" s="16">
         <f>SUM(G38:G40)</f>
@@ -26778,12 +26772,12 @@
         <v>1</v>
       </c>
       <c r="E43" s="23"/>
-      <c r="F43" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
+      <c r="F43" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
+      <c r="I43" s="67"/>
       <c r="J43" s="23"/>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -26822,42 +26816,42 @@
         <v>42</v>
       </c>
       <c r="G44" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H44" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I44" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H44" s="52" t="s">
+      <c r="J44" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I44" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J44" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M44" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="N44" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M44" s="52" t="s">
+      <c r="O44" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="N44" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="O44" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="P44" s="23"/>
       <c r="Q44" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R44" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S44" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R44" s="52" t="s">
+      <c r="T44" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S44" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T44" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U44" s="23"/>
       <c r="V44" s="62" t="str">
@@ -26865,10 +26859,10 @@
         <v>Metrics History State</v>
       </c>
       <c r="W44" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X44" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -26942,14 +26936,14 @@
       </c>
       <c r="U45" s="23"/>
       <c r="V45" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W45" s="43">
         <f>SUMPRODUCT(G45:I47, M45:O47) /$J$48</f>
         <v>0</v>
       </c>
       <c r="X45" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27023,14 +27017,14 @@
       </c>
       <c r="U46" s="23"/>
       <c r="V46" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W46" s="46">
         <f>SUMPRODUCT(R45:T47, M45:O47)</f>
         <v>0</v>
       </c>
       <c r="X46" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27104,14 +27098,14 @@
       </c>
       <c r="U47" s="23"/>
       <c r="V47" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W47" s="48" t="e">
         <f>1-W45/W46</f>
         <v>#DIV/0!</v>
       </c>
       <c r="X47" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27133,7 +27127,7 @@
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G48" s="16">
         <f t="shared" ref="G48:I48" si="65">SUM(G45:G47)</f>
@@ -27222,12 +27216,12 @@
         <v>0</v>
       </c>
       <c r="E50" s="23"/>
-      <c r="F50" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
+      <c r="F50" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" s="67"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="67"/>
       <c r="J50" s="23"/>
       <c r="K50" s="23"/>
       <c r="L50" s="23"/>
@@ -27266,42 +27260,42 @@
         <v>13</v>
       </c>
       <c r="G51" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H51" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I51" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="H51" s="52" t="s">
+      <c r="J51" s="53" t="s">
         <v>172</v>
-      </c>
-      <c r="I51" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="J51" s="53" t="s">
-        <v>174</v>
       </c>
       <c r="K51" s="23"/>
       <c r="L51" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M51" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="N51" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="M51" s="52" t="s">
+      <c r="O51" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="N51" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="O51" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="P51" s="23"/>
       <c r="Q51" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="R51" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="S51" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="R51" s="52" t="s">
+      <c r="T51" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="S51" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="T51" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="U51" s="23"/>
       <c r="V51" s="62" t="str">
@@ -27309,10 +27303,10 @@
         <v>Metrics Region</v>
       </c>
       <c r="W51" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X51" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27386,14 +27380,14 @@
       </c>
       <c r="U52" s="23"/>
       <c r="V52" s="40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W52" s="43">
         <f>SUMPRODUCT(G52:I54, M52:O54) /$J$55</f>
         <v>0</v>
       </c>
       <c r="X52" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27467,14 +27461,14 @@
       </c>
       <c r="U53" s="23"/>
       <c r="V53" s="40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W53" s="46">
         <f>SUMPRODUCT(R52:T54, M52:O54)</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="X53" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27548,14 +27542,14 @@
       </c>
       <c r="U54" s="23"/>
       <c r="V54" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W54" s="48">
         <f>1-W52/W53</f>
         <v>1</v>
       </c>
       <c r="X54" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -27577,7 +27571,7 @@
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G55" s="16">
         <f t="shared" ref="G55:I55" si="75">SUM(G52:G54)</f>
